--- a/education_forms/040_student_parent_handbook_acknowledgment_form--education_forms.xlsx
+++ b/education_forms/040_student_parent_handbook_acknowledgment_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Student Name</t>
+          <t>Student Name Label</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Student Grade</t>
+          <t>Student Grade Label</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Parent Name</t>
+          <t>Parent Name Label</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Parent Email</t>
+          <t>Parent Email Label</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Student Handbook</t>
+          <t>Student Handbook Label</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Attachments</t>
+          <t>Attachment Label</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Date Completed</t>
+          <t>Date Completed Label</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Signature</t>
+          <t>Signature Label</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Notes Label</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1165,129 +1165,44 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>student_grade_choices</t>
+          <t>student_parent_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>student</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Student</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>student_grade_choices</t>
+          <t>student_parent_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>parent</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>student_grade_choices</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>student_grade_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>student_grade_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>student_parent_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>student</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Student</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>student_parent_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>parent</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
         <is>
           <t>Parent</t>
         </is>
